--- a/customer_satisfaction_evaluation_forms/045_status_reacquisition_survey--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/045_status_reacquisition_survey--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1:_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1: 'Very Satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{2:_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2: 'Somewhat Satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{3:_'neutral'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{3: 'Neutral'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{4:_'somewhat_dissatisfied'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{4: 'Somewhat Dissatisfied'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{5:_'very_dissatisfied'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{5: 'Very Dissatisfied'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{1:_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{1: True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{2:_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{2: False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{1:_'new'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{1: 'New'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{2:_'returning'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{2: 'Returning'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{1:_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{1: 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{2:_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{2: 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{3:_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{3: 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{4:_'poor'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{4: 'Poor'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{1:_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{1: 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{2:_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{2: 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{3:_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{3: 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{4:_'poor'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{4: 'Poor'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{1:_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{1: 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{2:_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{2: 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{3:_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{3: 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{4:_'poor'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{4: 'Poor'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{1:_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{1: True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{2:_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{2: False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{1:_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{1: True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{2:_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{2: False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{1:_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{1: 'Very Satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{2:_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{2: 'Somewhat Satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{3:_'neutral'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{3: 'Neutral'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{4:_'somewhat_dissatisfied'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{4: 'Somewhat Dissatisfied'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{5:_'very_dissatisfied'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{5: 'Very Dissatisfied'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
